--- a/occupations_comparison.xlsx
+++ b/occupations_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/occupations_comparison.xlsx
+++ b/occupations_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>significant</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>marginally_significant</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -497,24 +492,21 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.272727272727273</v>
+        <v>2.120481927710844</v>
       </c>
       <c r="E2" t="n">
-        <v>1.458333333333333</v>
+        <v>1.670588235294118</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8143939393939397</v>
+        <v>0.4498936924167258</v>
       </c>
       <c r="G2" t="n">
-        <v>3.909668943020703</v>
+        <v>3.322079516257836</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003202906725035777</v>
+        <v>0.001101853268699424</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -535,138 +527,126 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.772727272727273</v>
+        <v>1.602409638554217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>1.011764705882353</v>
       </c>
       <c r="F3" t="n">
-        <v>1.272727272727273</v>
+        <v>0.5906449326718639</v>
       </c>
       <c r="G3" t="n">
-        <v>5.02978833658533</v>
+        <v>3.654035517015679</v>
       </c>
       <c r="H3" t="n">
-        <v>1.000443051942479e-05</v>
+        <v>0.0003555808358415839</v>
       </c>
       <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>receptionist</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>recepciós</t>
+          <t>ápoló</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>前台</t>
+          <t>护士</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6144578313253012</v>
       </c>
       <c r="E4" t="n">
-        <v>1.375</v>
+        <v>1.788235294117647</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6931818181818182</v>
+        <v>-1.173777462792346</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.611683272919604</v>
+        <v>-8.00209638496427</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01237725738399187</v>
+        <v>8.733665409687585e-13</v>
       </c>
       <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nurse</t>
+          <t>receptionist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ápoló</t>
+          <t>recepciós</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>护士</t>
+          <t>前台</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.6746987951807228</v>
       </c>
       <c r="E5" t="n">
-        <v>1.583333333333333</v>
+        <v>1.635294117647059</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.174242424242424</v>
+        <v>-0.9605953224663359</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.980736356109629</v>
+        <v>-7.793414214562848</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0004721380862215187</v>
+        <v>6.789313231930982e-13</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cashier</t>
+          <t>cleaner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pénztáros</t>
+          <t>takarító</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>收银员</t>
+          <t>保洁</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.045454545454545</v>
+        <v>0.9879518072289156</v>
       </c>
       <c r="E6" t="n">
-        <v>0.875</v>
+        <v>1.223529411764706</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1704545454545454</v>
+        <v>-0.2355776045357904</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7502582855355107</v>
+        <v>-1.357719666255729</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4574500137904128</v>
+        <v>0.1767626405900768</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -687,328 +667,301 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.454545454545455</v>
+        <v>1.36144578313253</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9962121212121213</v>
+        <v>0.5143869596031184</v>
       </c>
       <c r="G7" t="n">
-        <v>4.587243492317245</v>
+        <v>3.570973410072539</v>
       </c>
       <c r="H7" t="n">
-        <v>4.222435277709455e-05</v>
+        <v>0.0004686103327450436</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cleaner</t>
+          <t>cashier</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>takarító</t>
+          <t>pénztáros</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>保洁</t>
+          <t>收银员</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.136363636363636</v>
+        <v>0.9036144578313253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7083333333333334</v>
+        <v>1.129411764705882</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4280303030303031</v>
+        <v>-0.225797306874557</v>
       </c>
       <c r="G8" t="n">
-        <v>1.440618591769902</v>
+        <v>-1.7287258065906</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1576319806530823</v>
+        <v>0.08572572817157974</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>shop assistant</t>
+          <t>caregiver</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bolti eladó</t>
+          <t>gondozó</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>导购员</t>
+          <t>护工</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.7951807228915663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.141176470588235</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1212121212121212</v>
+        <v>-0.345995747696669</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5460373388053767</v>
+        <v>-2.083495456753595</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5881534369859585</v>
+        <v>0.03875872784085046</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>caregiver</t>
+          <t>HR personnel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gondozó</t>
+          <t>HR-es</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>护工</t>
+          <t>人事</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.192771084337349</v>
       </c>
       <c r="E10" t="n">
-        <v>0.625</v>
+        <v>0.6588235294117647</v>
       </c>
       <c r="F10" t="n">
-        <v>0.375</v>
+        <v>0.5339475549255847</v>
       </c>
       <c r="G10" t="n">
-        <v>1.354655785672191</v>
+        <v>3.970720316131799</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1835508305199453</v>
+        <v>0.0001065842259794784</v>
       </c>
       <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HR personnel</t>
+          <t>model</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HR-es</t>
+          <t>modell</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>人事</t>
+          <t>模特</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9545454545454546</v>
+        <v>1.08433734939759</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7529411764705882</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3712121212121212</v>
+        <v>0.3313961729270021</v>
       </c>
       <c r="G11" t="n">
-        <v>1.511105019686218</v>
+        <v>2.45997117006273</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1379154635688628</v>
+        <v>0.01493443392470924</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>shop assistant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>modell</t>
+          <t>bolti eladó</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>模特</t>
+          <t>导购员</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.045454545454545</v>
+        <v>0.7590361445783133</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.023529411764706</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7121212121212122</v>
+        <v>-0.2644932671863925</v>
       </c>
       <c r="G12" t="n">
-        <v>3.185238854850059</v>
+        <v>-1.98686915682735</v>
       </c>
       <c r="H12" t="n">
-        <v>0.003047683657907094</v>
+        <v>0.04862406232705102</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>accountant</t>
+          <t>secretary</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>könyvelő</t>
+          <t>titkár</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>会计</t>
+          <t>秘书</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>-0.04819277108433735</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>1.447058823529412</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-1.495251594613749</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-8.156699078811902</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4.181985648008155e-13</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dietitian</t>
+          <t>accountant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dietetikus</t>
+          <t>könyvelő</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>营养师</t>
+          <t>会计</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.7108433734939759</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.6352941176470588</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4734848484848484</v>
+        <v>0.07554925584691707</v>
       </c>
       <c r="G14" t="n">
-        <v>2.590566664590173</v>
+        <v>0.5933585467847534</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01306655515508556</v>
+        <v>0.5537602153375663</v>
       </c>
       <c r="I14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>secretary</t>
+          <t>dietitian</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>titkár</t>
+          <t>dietetikus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>秘书</t>
+          <t>营养师</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2272727272727273</v>
+        <v>0.7710843373493976</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.4352941176470588</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.185606060606061</v>
+        <v>0.3357902197023388</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.151097852083383</v>
+        <v>2.731125143361691</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0002721353303476533</v>
+        <v>0.00699545213529462</v>
       </c>
       <c r="I15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1029,24 +982,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.106060606060606</v>
+        <v>-0.5469879518072289</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5641784799800005</v>
+        <v>-4.368882058292442</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5762078195213023</v>
+        <v>2.193932430568303e-05</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1067,24 +1017,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.108433734939759</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.7294117647058823</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5416666666666666</v>
+        <v>-0.6209780297661233</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.113894473236767</v>
+        <v>-4.358682079841628</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0416603615807663</v>
+        <v>2.350036008789183e-05</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1105,252 +1052,231 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.75</v>
+        <v>-0.6352941176470588</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>1.550956768249468</v>
       </c>
       <c r="G18" t="n">
-        <v>7.312199986209629</v>
+        <v>12.22239203153393</v>
       </c>
       <c r="H18" t="n">
-        <v>5.736293580683683e-09</v>
+        <v>7.129289457222422e-25</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>waiter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>diák</t>
+          <t>pincér</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>服务员</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-0.5903614457831325</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.04166666666666666</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04166666666666666</v>
+        <v>-1.17859673990078</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9999999999999999</v>
+        <v>-8.211762950150245</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3277158061428587</v>
+        <v>8.594436382740733e-14</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>waiter</t>
+          <t>student</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pincér</t>
+          <t>diák</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>服务员</t>
+          <t>学生</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08333333333333333</v>
+        <v>-0.03529411764705882</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5833333333333334</v>
+        <v>0.03529411764705882</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.631147236438226</v>
+        <v>0.7627713759553691</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01372319612133357</v>
+        <v>0.4466954151317778</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>judge</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bíró</t>
+          <t>orvos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>法官</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1818181818181818</v>
+        <v>-0.4698795180722892</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.375</v>
+        <v>-0.1647058823529412</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1931818181818182</v>
+        <v>-0.305173635719348</v>
       </c>
       <c r="G21" t="n">
-        <v>1.137359285196932</v>
+        <v>-2.874735379663183</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2617076106771504</v>
+        <v>0.004581996108486566</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>judge</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>orvos</t>
+          <t>bíró</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>法官</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.5454545454545454</v>
+        <v>-0.3975903614457831</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2083333333333333</v>
+        <v>-0.3882352941176471</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.337121212121212</v>
+        <v>-0.009355067328136069</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.054339620052613</v>
+        <v>-0.07110419632723089</v>
       </c>
       <c r="H22" t="n">
-        <v>0.04627231293429205</v>
+        <v>0.9434050342195315</v>
       </c>
       <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>scientist</t>
+          <t>prosecutor</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tudós</t>
+          <t>ügyész</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>科学家</t>
+          <t>检察官</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.4090909090909091</v>
+        <v>-0.6506024096385542</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4583333333333333</v>
+        <v>-0.4588235294117647</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0492424242424242</v>
+        <v>-0.1917788802267895</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2675243827289994</v>
+        <v>-1.484535835751451</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7903159835620165</v>
+        <v>0.1396083011524245</v>
       </c>
       <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>prosecutor</t>
+          <t>scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ügyész</t>
+          <t>tudós</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>检察官</t>
+          <t>科学家</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.6818181818181818</v>
+        <v>-0.6746987951807228</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4166666666666667</v>
+        <v>-0.5647058823529412</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2651515151515151</v>
+        <v>-0.1099929128277817</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.29631838610589</v>
+        <v>-0.8940649979809082</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2025301752938543</v>
+        <v>0.3726239779686676</v>
       </c>
       <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1371,252 +1297,231 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.6818181818181818</v>
+        <v>-0.7469879518072289</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5</v>
+        <v>-0.5176470588235295</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1818181818181818</v>
+        <v>-0.2293408929836994</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8932259348678961</v>
+        <v>-1.737970696816207</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3767374182940921</v>
+        <v>0.08413597804779804</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gardener</t>
+          <t>professor</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>kertész</t>
+          <t>professzor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>园丁</t>
+          <t>教授</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.9090909090909091</v>
+        <v>-1</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4166666666666667</v>
+        <v>-0.3411764705882353</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4924242424242424</v>
+        <v>-0.6588235294117647</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.073820206781514</v>
+        <v>-5.245336574137148</v>
       </c>
       <c r="H26" t="n">
-        <v>0.04500389931624605</v>
+        <v>5.318357999391252e-07</v>
       </c>
       <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>professor</t>
+          <t>gardener</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>professzor</t>
+          <t>kertész</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>园丁</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.9090909090909091</v>
+        <v>-0.9397590361445783</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.4583333333333333</v>
+        <v>-0.4705882352941176</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4507575757575757</v>
+        <v>-0.4691708008504607</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.971422077450163</v>
+        <v>-3.307833027456024</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05578924006946497</v>
+        <v>0.00115672561351058</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
-      </c>
-      <c r="J27" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pathologist</t>
+          <t>director</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kórboncnok</t>
+          <t>rendező</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>法医</t>
+          <t>导演</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.7727272727272727</v>
+        <v>-0.8554216867469879</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7916666666666666</v>
+        <v>-0.6823529411764706</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01893939393939392</v>
+        <v>-0.1730687455705173</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07802656104019065</v>
+        <v>-1.349967216432064</v>
       </c>
       <c r="H28" t="n">
-        <v>0.938162136118182</v>
+        <v>0.1788649600202172</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>director</t>
+          <t>pathologist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rendező</t>
+          <t>kórboncnok</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>导演</t>
+          <t>法医</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.8636363636363636</v>
+        <v>-0.9759036144578314</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.7083333333333334</v>
+        <v>-0.6235294117647059</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1553030303030303</v>
+        <v>-0.3523742026931255</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7508952253053734</v>
+        <v>-2.415663707386808</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4567678185235475</v>
+        <v>0.01681449287254913</v>
       </c>
       <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>architect</t>
+          <t>chef</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>építész</t>
+          <t>szakács</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>建筑师</t>
+          <t>厨师</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1.181818181818182</v>
+        <v>-1.024096385542169</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7083333333333334</v>
+        <v>-1.047058823529412</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4734848484848485</v>
+        <v>0.02296243798724307</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.930481285265844</v>
+        <v>0.1767488894809764</v>
       </c>
       <c r="H30" t="n">
-        <v>0.06014376954219001</v>
+        <v>0.8599211387117324</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chef</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>szakács</t>
+          <t>mérnök</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>厨师</t>
+          <t>工程师</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.8636363636363636</v>
+        <v>-1.108433734939759</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.041666666666667</v>
+        <v>-0.9764705882352941</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1780303030303031</v>
+        <v>-0.131963146704465</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8264912815316227</v>
+        <v>-0.9653882378376112</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4129899911933281</v>
+        <v>0.3357726922627929</v>
       </c>
       <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1637,62 +1542,56 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.5</v>
+        <v>-1.626506024096386</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5416666666666666</v>
+        <v>-0.4588235294117647</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9583333333333334</v>
+        <v>-1.167682494684621</v>
       </c>
       <c r="G32" t="n">
-        <v>-4.2781625152861</v>
+        <v>-8.380282945858275</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0001002275601044132</v>
+        <v>3.051811734201534e-14</v>
       </c>
       <c r="I32" t="b">
-        <v>1</v>
-      </c>
-      <c r="J32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>engineer</t>
+          <t>police officer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mérnök</t>
+          <t>rendőr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>工程师</t>
+          <t>警察</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-1.181818181818182</v>
+        <v>-1.08433734939759</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.875</v>
+        <v>-1.035294117647059</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3068181818181819</v>
+        <v>-0.04904323175053138</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.227569452533109</v>
+        <v>-0.4134486897068587</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2261436495059367</v>
+        <v>0.6798795566093254</v>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1713,62 +1612,56 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-1.272727272727273</v>
+        <v>-1.265060240963855</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.875</v>
+        <v>-0.8823529411764706</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3977272727272727</v>
+        <v>-0.3827072997873848</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.868613756136638</v>
+        <v>-2.952737785809239</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06835182058184208</v>
+        <v>0.003608584058332616</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>police officer</t>
+          <t>architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rendőr</t>
+          <t>építész</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>警察</t>
+          <t>建筑师</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-1.363636363636364</v>
+        <v>-1.156626506024096</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.125</v>
+        <v>-1.117647058823529</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2386363636363635</v>
+        <v>-0.0389794472005669</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.138167796810742</v>
+        <v>-0.2655361394417408</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2618962651646959</v>
+        <v>0.7909327245687816</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1789,176 +1682,161 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-1.409090909090909</v>
+        <v>-1.27710843373494</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.083333333333333</v>
+        <v>-1.270588235294118</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3257575757575759</v>
+        <v>-0.006520198440822078</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.463305286973424</v>
+        <v>-0.04885723680729024</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1504996708915435</v>
+        <v>0.9610962846304726</v>
       </c>
       <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>worker</t>
+          <t>pilot</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>munkás</t>
+          <t>pilóta</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>工人</t>
+          <t>飞行员</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-1.545454545454545</v>
+        <v>-1.530120481927711</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.125</v>
+        <v>-1.247058823529412</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4204545454545454</v>
+        <v>-0.283061658398299</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.65843372970663</v>
+        <v>-2.200449028715968</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1046906003137016</v>
+        <v>0.02931490169293492</v>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pilot</t>
+          <t>worker</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pilóta</t>
+          <t>munkás</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>飞行员</t>
+          <t>工人</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-1.681818181818182</v>
+        <v>-1.63855421686747</v>
       </c>
       <c r="E38" t="n">
-        <v>-1</v>
+        <v>-1.188235294117647</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6818181818181819</v>
+        <v>-0.4503189227498228</v>
       </c>
       <c r="G38" t="n">
-        <v>-3.187230903160563</v>
+        <v>-2.948735962373466</v>
       </c>
       <c r="H38" t="n">
-        <v>0.002735590921450158</v>
+        <v>0.003659993088750398</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
-      </c>
-      <c r="J38" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lifeguard</t>
+          <t>soldier</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vízimentő</t>
+          <t>katona</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>救生员</t>
+          <t>军人</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.227272727272727</v>
+        <v>-1.759036144578313</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5</v>
+        <v>-1.082352941176471</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2727272727272727</v>
+        <v>-0.6766832034018426</v>
       </c>
       <c r="G39" t="n">
-        <v>1.021553816602953</v>
+        <v>-5.900058933355147</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3126708528207452</v>
+        <v>1.998514215716686e-08</v>
       </c>
       <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>soldier</t>
+          <t>lifeguard</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>katona</t>
+          <t>vízimentő</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>军人</t>
+          <t>救生员</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1.863636363636364</v>
+        <v>-1.301204819277108</v>
       </c>
       <c r="E40" t="n">
-        <v>-1</v>
+        <v>-1.576470588235294</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.8636363636363635</v>
+        <v>0.2752657689581857</v>
       </c>
       <c r="G40" t="n">
-        <v>-4.086543426949811</v>
+        <v>1.962868295682484</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00018377507992935</v>
+        <v>0.05147273349677548</v>
       </c>
       <c r="I40" t="b">
-        <v>1</v>
-      </c>
-      <c r="J40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1979,24 +1857,21 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.954545454545455</v>
+        <v>-1.771084337349398</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.791666666666667</v>
+        <v>-1.752941176470588</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.1628787878787878</v>
+        <v>-0.01814316087880941</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9050529619874194</v>
+        <v>-0.1354909144806252</v>
       </c>
       <c r="H41" t="n">
-        <v>0.370786175219575</v>
+        <v>0.8923946433320897</v>
       </c>
       <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2017,25 +1892,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-2.272727272727273</v>
+        <v>-2.144578313253012</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.791666666666667</v>
+        <v>-1.788235294117647</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.4810606060606062</v>
+        <v>-0.3563430191353649</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.1860799100449</v>
+        <v>-2.584753311295846</v>
       </c>
       <c r="H42" t="n">
-        <v>0.03429839325138778</v>
+        <v>0.01060593522863386</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
-      </c>
-      <c r="J42" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
